--- a/data/nzd0064/nzd0064.xlsx
+++ b/data/nzd0064/nzd0064.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N365"/>
+  <dimension ref="A1:N367"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17958,6 +17958,102 @@
         <v>389.15</v>
       </c>
       <c r="N365" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:11:00+00:00</t>
+        </is>
+      </c>
+      <c r="B366" t="n">
+        <v>374.77</v>
+      </c>
+      <c r="C366" t="n">
+        <v>378.51</v>
+      </c>
+      <c r="D366" t="n">
+        <v>383.32</v>
+      </c>
+      <c r="E366" t="n">
+        <v>380.66</v>
+      </c>
+      <c r="F366" t="n">
+        <v>378.78</v>
+      </c>
+      <c r="G366" t="n">
+        <v>379.54</v>
+      </c>
+      <c r="H366" t="n">
+        <v>377.27</v>
+      </c>
+      <c r="I366" t="n">
+        <v>369.65</v>
+      </c>
+      <c r="J366" t="n">
+        <v>380.01</v>
+      </c>
+      <c r="K366" t="n">
+        <v>371.56</v>
+      </c>
+      <c r="L366" t="n">
+        <v>381.31</v>
+      </c>
+      <c r="M366" t="n">
+        <v>389.14</v>
+      </c>
+      <c r="N366" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B367" t="n">
+        <v>376.03</v>
+      </c>
+      <c r="C367" t="n">
+        <v>380.12</v>
+      </c>
+      <c r="D367" t="n">
+        <v>384.73</v>
+      </c>
+      <c r="E367" t="n">
+        <v>381.93</v>
+      </c>
+      <c r="F367" t="n">
+        <v>380.21</v>
+      </c>
+      <c r="G367" t="n">
+        <v>380.98</v>
+      </c>
+      <c r="H367" t="n">
+        <v>378.89</v>
+      </c>
+      <c r="I367" t="n">
+        <v>371.17</v>
+      </c>
+      <c r="J367" t="n">
+        <v>382.02</v>
+      </c>
+      <c r="K367" t="n">
+        <v>372.74</v>
+      </c>
+      <c r="L367" t="n">
+        <v>384.1</v>
+      </c>
+      <c r="M367" t="n">
+        <v>390.09</v>
+      </c>
+      <c r="N367" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -17974,7 +18070,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B372"/>
+  <dimension ref="A1:B374"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21697,6 +21793,26 @@
       </c>
       <c r="B372" t="n">
         <v>0.86</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B373" t="n">
+        <v>-0.38</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B374" t="n">
+        <v>0.43</v>
       </c>
     </row>
   </sheetData>
@@ -21865,28 +21981,28 @@
         <v>0.0688</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.02150144314563095</v>
+        <v>-0.03004023181485883</v>
       </c>
       <c r="J2" t="n">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="K2" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002379036287237124</v>
+        <v>0.004556768195500216</v>
       </c>
       <c r="M2" t="n">
-        <v>2.336302322496836</v>
+        <v>2.366228321684939</v>
       </c>
       <c r="N2" t="n">
-        <v>10.42556324947163</v>
+        <v>10.67811744898365</v>
       </c>
       <c r="O2" t="n">
-        <v>3.228864080365049</v>
+        <v>3.267738889352032</v>
       </c>
       <c r="P2" t="n">
-        <v>383.5101626674499</v>
+        <v>383.6036003187292</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -21947,28 +22063,28 @@
         <v>0.1268</v>
       </c>
       <c r="I3" t="n">
-        <v>0.009635879334262356</v>
+        <v>0.005256366748993769</v>
       </c>
       <c r="J3" t="n">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="K3" t="n">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0006175810587057962</v>
+        <v>0.0001842563585716661</v>
       </c>
       <c r="M3" t="n">
-        <v>2.08766173985044</v>
+        <v>2.098807685486782</v>
       </c>
       <c r="N3" t="n">
-        <v>8.192712563551947</v>
+        <v>8.233970333302832</v>
       </c>
       <c r="O3" t="n">
-        <v>2.86229148822267</v>
+        <v>2.869489559713161</v>
       </c>
       <c r="P3" t="n">
-        <v>382.9769532428779</v>
+        <v>383.0242900740715</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -22029,28 +22145,28 @@
         <v>0.1164</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0007314828866350804</v>
+        <v>-0.003387732291410734</v>
       </c>
       <c r="J4" t="n">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="K4" t="n">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="L4" t="n">
-        <v>3.373385978888699e-06</v>
+        <v>7.263616546027141e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>2.198578047467225</v>
+        <v>2.207187306497396</v>
       </c>
       <c r="N4" t="n">
-        <v>8.648645867806573</v>
+        <v>8.677092033445398</v>
       </c>
       <c r="O4" t="n">
-        <v>2.940858015580925</v>
+        <v>2.945690417108593</v>
       </c>
       <c r="P4" t="n">
-        <v>387.6899805649095</v>
+        <v>387.7345041838819</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -22111,28 +22227,28 @@
         <v>0.1182</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.08208469743429424</v>
+        <v>-0.08374600382091266</v>
       </c>
       <c r="J5" t="n">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="K5" t="n">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03675084441318821</v>
+        <v>0.03861052561608447</v>
       </c>
       <c r="M5" t="n">
-        <v>2.424308104053474</v>
+        <v>2.419074429055558</v>
       </c>
       <c r="N5" t="n">
-        <v>9.62948349564536</v>
+        <v>9.590965450133018</v>
       </c>
       <c r="O5" t="n">
-        <v>3.103140908119604</v>
+        <v>3.096928389571354</v>
       </c>
       <c r="P5" t="n">
-        <v>384.9918123860869</v>
+        <v>385.0097671699394</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -22193,28 +22309,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.05683312333029564</v>
+        <v>-0.0599672950649591</v>
       </c>
       <c r="J6" t="n">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="K6" t="n">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02111998809031879</v>
+        <v>0.02362209173859642</v>
       </c>
       <c r="M6" t="n">
-        <v>2.161837088512369</v>
+        <v>2.165736744952621</v>
       </c>
       <c r="N6" t="n">
-        <v>8.162930789567371</v>
+        <v>8.163361032296052</v>
       </c>
       <c r="O6" t="n">
-        <v>2.857084316145985</v>
+        <v>2.857159609174127</v>
       </c>
       <c r="P6" t="n">
-        <v>383.8322263718463</v>
+        <v>383.8661019524412</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -22275,28 +22391,28 @@
         <v>0.1432</v>
       </c>
       <c r="I7" t="n">
-        <v>0.05171836027737989</v>
+        <v>0.04752110191888831</v>
       </c>
       <c r="J7" t="n">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="K7" t="n">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01414635332302894</v>
+        <v>0.01202846045335104</v>
       </c>
       <c r="M7" t="n">
-        <v>2.5464521180356</v>
+        <v>2.552807940107546</v>
       </c>
       <c r="N7" t="n">
-        <v>10.16400138658547</v>
+        <v>10.18703706997453</v>
       </c>
       <c r="O7" t="n">
-        <v>3.188103101624141</v>
+        <v>3.191713813921062</v>
       </c>
       <c r="P7" t="n">
-        <v>382.6249889937281</v>
+        <v>382.6703561802724</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -22357,28 +22473,28 @@
         <v>0.1037</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.004167252355308881</v>
+        <v>-0.005130854226833785</v>
       </c>
       <c r="J8" t="n">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="K8" t="n">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0001046879830489678</v>
+        <v>0.0001605831197245555</v>
       </c>
       <c r="M8" t="n">
-        <v>2.316797233606037</v>
+        <v>2.308085580422309</v>
       </c>
       <c r="N8" t="n">
-        <v>9.044083762916298</v>
+        <v>9.002232129493674</v>
       </c>
       <c r="O8" t="n">
-        <v>3.007338318665909</v>
+        <v>3.000371998518462</v>
       </c>
       <c r="P8" t="n">
-        <v>379.0550292346857</v>
+        <v>379.0654411519905</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -22439,28 +22555,28 @@
         <v>0.09429999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0290437046347843</v>
+        <v>0.02666950181785148</v>
       </c>
       <c r="J9" t="n">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="K9" t="n">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="L9" t="n">
-        <v>0.004373895764342106</v>
+        <v>0.003727756885790634</v>
       </c>
       <c r="M9" t="n">
-        <v>2.524025160540907</v>
+        <v>2.520885885582449</v>
       </c>
       <c r="N9" t="n">
-        <v>10.46981827523063</v>
+        <v>10.44000599807266</v>
       </c>
       <c r="O9" t="n">
-        <v>3.235709856465909</v>
+        <v>3.231099812459011</v>
       </c>
       <c r="P9" t="n">
-        <v>371.7531641973326</v>
+        <v>371.7788245177213</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -22521,28 +22637,28 @@
         <v>0.1037</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.01757348234371699</v>
+        <v>-0.02164687595111323</v>
       </c>
       <c r="J10" t="n">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="K10" t="n">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="L10" t="n">
-        <v>0.001942719862172315</v>
+        <v>0.002955910683051455</v>
       </c>
       <c r="M10" t="n">
-        <v>2.257215743560324</v>
+        <v>2.267861431549937</v>
       </c>
       <c r="N10" t="n">
-        <v>8.651038010632321</v>
+        <v>8.680685160029944</v>
       </c>
       <c r="O10" t="n">
-        <v>2.941264695778386</v>
+        <v>2.946300249470502</v>
       </c>
       <c r="P10" t="n">
-        <v>385.1343063493097</v>
+        <v>385.1783330496302</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -22603,28 +22719,28 @@
         <v>0.1052</v>
       </c>
       <c r="I11" t="n">
-        <v>0.06432375090314833</v>
+        <v>0.056263834619074</v>
       </c>
       <c r="J11" t="n">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="K11" t="n">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01660291390603341</v>
+        <v>0.01264913337506934</v>
       </c>
       <c r="M11" t="n">
-        <v>2.706155228805182</v>
+        <v>2.725580763390673</v>
       </c>
       <c r="N11" t="n">
-        <v>13.36271171293753</v>
+        <v>13.570938664072</v>
       </c>
       <c r="O11" t="n">
-        <v>3.655504303504173</v>
+        <v>3.683875495191443</v>
       </c>
       <c r="P11" t="n">
-        <v>377.6308907543247</v>
+        <v>377.7180126902655</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -22685,28 +22801,28 @@
         <v>0.056</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.03420466599055236</v>
+        <v>-0.04380251197186633</v>
       </c>
       <c r="J12" t="n">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="K12" t="n">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="L12" t="n">
-        <v>0.004669188857615914</v>
+        <v>0.007507511175891768</v>
       </c>
       <c r="M12" t="n">
-        <v>2.8239607649624</v>
+        <v>2.859186017255205</v>
       </c>
       <c r="N12" t="n">
-        <v>13.53487541843129</v>
+        <v>13.86506328168367</v>
       </c>
       <c r="O12" t="n">
-        <v>3.678977496320314</v>
+        <v>3.723582049812206</v>
       </c>
       <c r="P12" t="n">
-        <v>392.1824215329585</v>
+        <v>392.2865658147127</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -22767,28 +22883,28 @@
         <v>0.0634</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1281800339372439</v>
+        <v>-0.1341667239636382</v>
       </c>
       <c r="J13" t="n">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="K13" t="n">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="L13" t="n">
-        <v>0.08107125751712596</v>
+        <v>0.08793482236828665</v>
       </c>
       <c r="M13" t="n">
-        <v>2.567444029221052</v>
+        <v>2.580660830943923</v>
       </c>
       <c r="N13" t="n">
-        <v>10.10678990423702</v>
+        <v>10.20580334895222</v>
       </c>
       <c r="O13" t="n">
-        <v>3.179117787097078</v>
+        <v>3.194652304860769</v>
       </c>
       <c r="P13" t="n">
-        <v>398.4013551458696</v>
+        <v>398.4663176180204</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -22830,7 +22946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N365"/>
+  <dimension ref="A1:N367"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49089,6 +49205,150 @@
         </is>
       </c>
     </row>
+    <row r="366">
+      <c r="A366" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:11:00+00:00</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>-35.25714966120632,174.13138477821894</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>-35.25777796617521,174.13172516787708</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>-35.25830453870326,174.13228034352952</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>-35.25878817970924,174.13291538263744</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>-35.25923200685001,174.13361091172027</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>-35.259596368648694,174.13436097581464</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>-35.259878253657426,174.13516494028448</t>
+        </is>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>-35.260147850512475,174.1360002743987</t>
+        </is>
+      </c>
+      <c r="J366" t="inlineStr">
+        <is>
+          <t>-35.260343956931116,174.13685526708827</t>
+        </is>
+      </c>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>-35.26057746395622,174.137692991065</t>
+        </is>
+      </c>
+      <c r="L366" t="inlineStr">
+        <is>
+          <t>-35.26066305469469,174.13859755913393</t>
+        </is>
+      </c>
+      <c r="M366" t="inlineStr">
+        <is>
+          <t>-35.260842751722585,174.1394762781412</t>
+        </is>
+      </c>
+      <c r="N366" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>-35.257145485767744,174.13139765839765</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>-35.25777078219388,174.13174054542887</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>-35.25829581042239,174.13229161162195</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>-35.258779222741445,174.13292407899507</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>-35.259221267437965,174.13361960879067</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>-35.25958470584918,174.13436792988293</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>-35.25986440393988,174.13517059505466</t>
+        </is>
+      </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>-35.260134910015,174.13600577384793</t>
+        </is>
+      </c>
+      <c r="J367" t="inlineStr">
+        <is>
+          <t>-35.26032667714072,174.13686192395772</t>
+        </is>
+      </c>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>-35.260567085773765,174.13769584402684</t>
+        </is>
+      </c>
+      <c r="L367" t="inlineStr">
+        <is>
+          <t>-35.260638883028825,174.13860604705425</t>
+        </is>
+      </c>
+      <c r="M367" t="inlineStr">
+        <is>
+          <t>-35.26083466112395,174.13947970553127</t>
+        </is>
+      </c>
+      <c r="N367" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0064/nzd0064.xlsx
+++ b/data/nzd0064/nzd0064.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N367"/>
+  <dimension ref="A1:N368"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18054,6 +18054,54 @@
         <v>390.09</v>
       </c>
       <c r="N367" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:21+00:00</t>
+        </is>
+      </c>
+      <c r="B368" t="n">
+        <v>374.33</v>
+      </c>
+      <c r="C368" t="n">
+        <v>380.36</v>
+      </c>
+      <c r="D368" t="n">
+        <v>385.84</v>
+      </c>
+      <c r="E368" t="n">
+        <v>382.03</v>
+      </c>
+      <c r="F368" t="n">
+        <v>381.46</v>
+      </c>
+      <c r="G368" t="n">
+        <v>381.58</v>
+      </c>
+      <c r="H368" t="n">
+        <v>380.64</v>
+      </c>
+      <c r="I368" t="n">
+        <v>371.95</v>
+      </c>
+      <c r="J368" t="n">
+        <v>386.15</v>
+      </c>
+      <c r="K368" t="n">
+        <v>377.03</v>
+      </c>
+      <c r="L368" t="n">
+        <v>388.39</v>
+      </c>
+      <c r="M368" t="n">
+        <v>390.93</v>
+      </c>
+      <c r="N368" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -18070,7 +18118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B374"/>
+  <dimension ref="A1:B375"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21813,6 +21861,16 @@
       </c>
       <c r="B374" t="n">
         <v>0.43</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B375" t="n">
+        <v>-0.5</v>
       </c>
     </row>
   </sheetData>
@@ -21981,28 +22039,28 @@
         <v>0.0688</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.03004023181485883</v>
+        <v>-0.03483632417704321</v>
       </c>
       <c r="J2" t="n">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="K2" t="n">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004556768195500216</v>
+        <v>0.00604678344273446</v>
       </c>
       <c r="M2" t="n">
-        <v>2.366228321684939</v>
+        <v>2.384114465236252</v>
       </c>
       <c r="N2" t="n">
-        <v>10.67811744898365</v>
+        <v>10.84435144861816</v>
       </c>
       <c r="O2" t="n">
-        <v>3.267738889352032</v>
+        <v>3.293076289522937</v>
       </c>
       <c r="P2" t="n">
-        <v>383.6036003187292</v>
+        <v>383.6562901417996</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -22063,28 +22121,28 @@
         <v>0.1268</v>
       </c>
       <c r="I3" t="n">
-        <v>0.005256366748993769</v>
+        <v>0.003689240165063539</v>
       </c>
       <c r="J3" t="n">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="K3" t="n">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0001842563585716661</v>
+        <v>9.111670546446682e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>2.098807685486782</v>
+        <v>2.101187132805487</v>
       </c>
       <c r="N3" t="n">
-        <v>8.233970333302832</v>
+        <v>8.232800151375546</v>
       </c>
       <c r="O3" t="n">
-        <v>2.869489559713161</v>
+        <v>2.869285651756469</v>
       </c>
       <c r="P3" t="n">
-        <v>383.0242900740715</v>
+        <v>383.0412969036379</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -22145,28 +22203,28 @@
         <v>0.1164</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.003387732291410734</v>
+        <v>-0.004393831775732837</v>
       </c>
       <c r="J4" t="n">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="K4" t="n">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="L4" t="n">
-        <v>7.263616546027141e-05</v>
+        <v>0.0001228332387859243</v>
       </c>
       <c r="M4" t="n">
-        <v>2.207187306497396</v>
+        <v>2.206165990060284</v>
       </c>
       <c r="N4" t="n">
-        <v>8.677092033445398</v>
+        <v>8.662213762231369</v>
       </c>
       <c r="O4" t="n">
-        <v>2.945690417108593</v>
+        <v>2.943163903392295</v>
       </c>
       <c r="P4" t="n">
-        <v>387.7345041838819</v>
+        <v>387.7454226142322</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -22227,28 +22285,28 @@
         <v>0.1182</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.08374600382091266</v>
+        <v>-0.08414738192927471</v>
       </c>
       <c r="J5" t="n">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="K5" t="n">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03861052561608447</v>
+        <v>0.03919989232416721</v>
       </c>
       <c r="M5" t="n">
-        <v>2.419074429055558</v>
+        <v>2.414395908480905</v>
       </c>
       <c r="N5" t="n">
-        <v>9.590965450133018</v>
+        <v>9.566227044629285</v>
       </c>
       <c r="O5" t="n">
-        <v>3.096928389571354</v>
+        <v>3.092931787904364</v>
       </c>
       <c r="P5" t="n">
-        <v>385.0097671699394</v>
+        <v>385.014123020418</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -22309,28 +22367,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0599672950649591</v>
+        <v>-0.06040582328745871</v>
       </c>
       <c r="J6" t="n">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="K6" t="n">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02362209173859642</v>
+        <v>0.02410456795846427</v>
       </c>
       <c r="M6" t="n">
-        <v>2.165736744952621</v>
+        <v>2.162016392003504</v>
       </c>
       <c r="N6" t="n">
-        <v>8.163361032296052</v>
+        <v>8.142782742952619</v>
       </c>
       <c r="O6" t="n">
-        <v>2.857159609174127</v>
+        <v>2.853556157315398</v>
       </c>
       <c r="P6" t="n">
-        <v>383.8661019524412</v>
+        <v>383.8708609647741</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -22391,28 +22449,28 @@
         <v>0.1432</v>
       </c>
       <c r="I7" t="n">
-        <v>0.04752110191888831</v>
+        <v>0.04619568731043124</v>
       </c>
       <c r="J7" t="n">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="K7" t="n">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01202846045335104</v>
+        <v>0.0114290286815909</v>
       </c>
       <c r="M7" t="n">
-        <v>2.552807940107546</v>
+        <v>2.552219774447761</v>
       </c>
       <c r="N7" t="n">
-        <v>10.18703706997453</v>
+        <v>10.17449108380397</v>
       </c>
       <c r="O7" t="n">
-        <v>3.191713813921062</v>
+        <v>3.189747808809337</v>
       </c>
       <c r="P7" t="n">
-        <v>382.6703561802724</v>
+        <v>382.6847398941231</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -22473,28 +22531,28 @@
         <v>0.1037</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.005130854226833785</v>
+        <v>-0.004172055377068161</v>
       </c>
       <c r="J8" t="n">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="K8" t="n">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0001605831197245555</v>
+        <v>0.0001067615635452768</v>
       </c>
       <c r="M8" t="n">
-        <v>2.308085580422309</v>
+        <v>2.30719627704697</v>
       </c>
       <c r="N8" t="n">
-        <v>9.002232129493674</v>
+        <v>8.985663135190434</v>
       </c>
       <c r="O8" t="n">
-        <v>3.000371998518462</v>
+        <v>2.997609570172612</v>
       </c>
       <c r="P8" t="n">
-        <v>379.0654411519905</v>
+        <v>379.0550360393508</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -22555,28 +22613,28 @@
         <v>0.09429999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02666950181785148</v>
+        <v>0.02636326470627057</v>
       </c>
       <c r="J9" t="n">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="K9" t="n">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="L9" t="n">
-        <v>0.003727756885790634</v>
+        <v>0.003665768960495974</v>
       </c>
       <c r="M9" t="n">
-        <v>2.520885885582449</v>
+        <v>2.515373240306619</v>
       </c>
       <c r="N9" t="n">
-        <v>10.44000599807266</v>
+        <v>10.41237117363774</v>
       </c>
       <c r="O9" t="n">
-        <v>3.231099812459011</v>
+        <v>3.226820598303807</v>
       </c>
       <c r="P9" t="n">
-        <v>371.7788245177213</v>
+        <v>371.7821478755259</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -22637,28 +22695,28 @@
         <v>0.1037</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.02164687595111323</v>
+        <v>-0.02077596604967106</v>
       </c>
       <c r="J10" t="n">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="K10" t="n">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="L10" t="n">
-        <v>0.002955910683051455</v>
+        <v>0.002738699195259153</v>
       </c>
       <c r="M10" t="n">
-        <v>2.267861431549937</v>
+        <v>2.265246110567499</v>
       </c>
       <c r="N10" t="n">
-        <v>8.680685160029944</v>
+        <v>8.663599839076596</v>
       </c>
       <c r="O10" t="n">
-        <v>2.946300249470502</v>
+        <v>2.943399367920805</v>
       </c>
       <c r="P10" t="n">
-        <v>385.1783330496302</v>
+        <v>385.1688817287135</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -22719,28 +22777,28 @@
         <v>0.1052</v>
       </c>
       <c r="I11" t="n">
-        <v>0.056263834619074</v>
+        <v>0.05502964669471529</v>
       </c>
       <c r="J11" t="n">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="K11" t="n">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01264913337506934</v>
+        <v>0.01217134072079007</v>
       </c>
       <c r="M11" t="n">
-        <v>2.725580763390673</v>
+        <v>2.723401588303501</v>
       </c>
       <c r="N11" t="n">
-        <v>13.570938664072</v>
+        <v>13.54715030794169</v>
       </c>
       <c r="O11" t="n">
-        <v>3.683875495191443</v>
+        <v>3.680645365685438</v>
       </c>
       <c r="P11" t="n">
-        <v>377.7180126902655</v>
+        <v>377.7314063904923</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -22801,28 +22859,28 @@
         <v>0.056</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.04380251197186633</v>
+        <v>-0.04532171635197664</v>
       </c>
       <c r="J12" t="n">
+        <v>367</v>
+      </c>
+      <c r="K12" t="n">
         <v>366</v>
       </c>
-      <c r="K12" t="n">
-        <v>365</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.007507511175891768</v>
+        <v>0.008072351655511345</v>
       </c>
       <c r="M12" t="n">
-        <v>2.859186017255205</v>
+        <v>2.859427568869951</v>
       </c>
       <c r="N12" t="n">
-        <v>13.86506328168367</v>
+        <v>13.84704112654189</v>
       </c>
       <c r="O12" t="n">
-        <v>3.723582049812206</v>
+        <v>3.721161260486018</v>
       </c>
       <c r="P12" t="n">
-        <v>392.2865658147127</v>
+        <v>392.3031163130076</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -22883,28 +22941,28 @@
         <v>0.0634</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1341667239636382</v>
+        <v>-0.1363575719912945</v>
       </c>
       <c r="J13" t="n">
+        <v>367</v>
+      </c>
+      <c r="K13" t="n">
         <v>366</v>
       </c>
-      <c r="K13" t="n">
-        <v>365</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.08793482236828665</v>
+        <v>0.09075792951052442</v>
       </c>
       <c r="M13" t="n">
-        <v>2.580660830943923</v>
+        <v>2.583566258127079</v>
       </c>
       <c r="N13" t="n">
-        <v>10.20580334895222</v>
+        <v>10.21922177024222</v>
       </c>
       <c r="O13" t="n">
-        <v>3.194652304860769</v>
+        <v>3.196751752989621</v>
       </c>
       <c r="P13" t="n">
-        <v>398.4663176180204</v>
+        <v>398.4901851285547</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -22946,7 +23004,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N367"/>
+  <dimension ref="A1:N368"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49349,6 +49407,78 @@
         </is>
       </c>
     </row>
+    <row r="368">
+      <c r="A368" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:21+00:00</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>-35.25715111929568,174.13138028037844</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>-35.25776971128967,174.1317428377345</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>-35.25828893922184,174.1323004822462</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>-35.25877851746838,174.13292476374758</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>-35.25921187983954,174.13362721112313</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>-35.25957984634927,174.13437082741078</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>-35.259849442824965,174.13517670360056</t>
+        </is>
+      </c>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>-35.26012826949646,174.13600859593305</t>
+        </is>
+      </c>
+      <c r="J368" t="inlineStr">
+        <is>
+          <t>-35.260291171898665,174.13687560199435</t>
+        </is>
+      </c>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>-35.26052935492338,174.13770621622965</t>
+        </is>
+      </c>
+      <c r="L368" t="inlineStr">
+        <is>
+          <t>-35.2606017158425,174.13861909836316</t>
+        </is>
+      </c>
+      <c r="M368" t="inlineStr">
+        <is>
+          <t>-35.2608275073314,174.13948273606513</t>
+        </is>
+      </c>
+      <c r="N368" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
